--- a/lib/__tests__/fixtures/NRM1_v5_4_one_sheet_layout.xlsx
+++ b/lib/__tests__/fixtures/NRM1_v5_4_one_sheet_layout.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.2 (September 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">Single source of truth for the scope of works and its prices, in three sheets. Prepared by Nabil Kayali.</t>
+    <t xml:space="preserve">Single source of truth for the scope of works and its prices, in three sheets. Prepared by Projento.</t>
   </si>
   <si>
     <t xml:space="preserve">THE THREE SHEETS</t>
@@ -3033,7 +3033,7 @@
     <t xml:space="preserve">Owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Nabil Kayali</t>
+    <t xml:space="preserve">Projento</t>
   </si>
   <si>
     <t xml:space="preserve">▶ building_uses</t>
